--- a/Result/profitability/1528.xlsx
+++ b/Result/profitability/1528.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.135</v>
+        <v>-0.14875</v>
       </c>
       <c r="N2" t="n">
-        <v>28.69375</v>
+        <v>29.3475</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0725</v>
+        <v>-0.09749999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>28.24375</v>
+        <v>28.2375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.15</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0225</v>
+        <v>-0.08499999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>27.2625</v>
+        <v>27.34875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.09</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.03999999999999999</v>
+        <v>-0.01374999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>26.9575</v>
+        <v>26.49375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04625000000000001</v>
+        <v>-0.01999999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>25.23375</v>
+        <v>25.0525</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02250000000000001</v>
+        <v>-0.05624999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>24.16375</v>
+        <v>23.8925</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01750000000000001</v>
+        <v>-0.01999999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>23.4</v>
+        <v>23.25125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1528</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>777</v>
+      </c>
+      <c r="D75" t="n">
+        <v>550</v>
+      </c>
+      <c r="E75" t="n">
+        <v>228</v>
+      </c>
+      <c r="F75" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-3.09%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-44</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-86</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.1925</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.61125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.189999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03905480800787653</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3181818181818182</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.710000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1124583207032435</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
